--- a/output/pdf_financials_xlsx/LUX.xlsx
+++ b/output/pdf_financials_xlsx/LUX.xlsx
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>1.593996</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>1.970008</v>
       </c>
     </row>
     <row r="92">
@@ -2910,7 +2910,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>1.593996</v>
       </c>

--- a/output/pdf_financials_xlsx/LUX.xlsx
+++ b/output/pdf_financials_xlsx/LUX.xlsx
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.283982</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.127631</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.283982</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.127631</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.362332</v>
+        <v>0.07835</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.136747</v>
+        <v>0.009116000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">

--- a/output/pdf_financials_xlsx/LUX.xlsx
+++ b/output/pdf_financials_xlsx/LUX.xlsx
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1.145846</v>
+        <v>0.029724</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.390241</v>
+        <v>0.030097</v>
       </c>
     </row>
     <row r="29">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.286394</v>
+        <v>-4.402516</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.723076</v>
+        <v>-4.08322</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-117.6424220837681</v>
+        <v>-157.5960294178186</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-209.5782999002549</v>
+        <v>-314.2601623012795</v>
       </c>
     </row>
     <row r="31">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.009660999999999999</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.011191</v>
       </c>
     </row>
     <row r="71">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.009660999999999999</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.011191</v>
       </c>
     </row>
     <row r="72">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>4.219918</v>
+        <v>4.210257</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>7.977284</v>
+        <v>7.966093</v>
       </c>
     </row>
     <row r="76">
@@ -1468,15 +1468,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.005234336946963667</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>-0.007043428074395619</v>
       </c>
     </row>
     <row r="81">
@@ -1727,10 +1723,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.029724</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.030097</v>
       </c>
     </row>
     <row r="101">
@@ -1740,7 +1736,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.106781</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -1805,7 +1801,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.029321</v>
+        <v>0.07746</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>1.012819</v>
@@ -1857,10 +1853,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.219426</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.311022</v>
       </c>
     </row>
     <row r="111">
@@ -2644,7 +2640,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.009660999999999999</v>
       </c>
@@ -3050,7 +3050,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.029724</v>
       </c>
@@ -3182,7 +3186,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.219426</v>
       </c>
@@ -3256,7 +3264,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>0.172509</v>
       </c>
@@ -3382,7 +3394,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>-0.06572799999999999</v>
       </c>
@@ -4100,7 +4116,11 @@
           <t>Amortization expense 12</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.029724</v>
       </c>
@@ -4808,7 +4828,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>0.02338</v>
       </c>
